--- a/output/pdf_financials_xlsx/SASQ.xlsx
+++ b/output/pdf_financials_xlsx/SASQ.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022442</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008916</v>
       </c>
     </row>
     <row r="13">
@@ -882,10 +882,10 @@
         <v>-0.345224</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.289422</v>
+        <v>-0.26698</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.444922</v>
+        <v>-0.436006</v>
       </c>
     </row>
     <row r="28">
@@ -914,10 +914,10 @@
         <v>-0.345224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.289422</v>
+        <v>-0.26698</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.444922</v>
+        <v>-0.436006</v>
       </c>
     </row>
     <row r="30">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">

--- a/output/pdf_financials_xlsx/SASQ.xlsx
+++ b/output/pdf_financials_xlsx/SASQ.xlsx
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003977</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.017809</v>
@@ -3757,7 +3757,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>-0.003977</v>
       </c>
